--- a/frontend/test_data/header_detection/Wide_Mixed_Types_Top_Test.xlsx
+++ b/frontend/test_data/header_detection/Wide_Mixed_Types_Top_Test.xlsx
@@ -16735,7 +16735,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N200"/>
+  <dimension ref="A1:M200"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -16763,21 +16763,18 @@
         <v>Mixed Data Penalty</v>
       </c>
       <c r="I1" t="str">
-        <v>Search Booster (Pivoted)</v>
+        <v>Orphan Header Penalty</v>
       </c>
       <c r="J1" t="str">
-        <v>Orphan Header Penalty</v>
+        <v>Duplicates Penalty</v>
       </c>
       <c r="K1" t="str">
-        <v>Duplicates Penalty</v>
+        <v>FILLED CELLS</v>
       </c>
       <c r="L1" t="str">
-        <v>FILLED CELLS</v>
+        <v>TOTAL RAW SCORE</v>
       </c>
       <c r="M1" t="str">
-        <v>TOTAL RAW SCORE</v>
-      </c>
-      <c r="N1" t="str">
         <v>NORMALIZED SCORE (%)</v>
       </c>
     </row>
@@ -16813,15 +16810,12 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L2">
-        <v>12</v>
+        <v>-68</v>
       </c>
       <c r="M2">
-        <v>-68</v>
-      </c>
-      <c r="N2">
         <v>0</v>
       </c>
     </row>
@@ -16857,15 +16851,12 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L3">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="M3">
-        <v>21</v>
-      </c>
-      <c r="N3">
         <v>21</v>
       </c>
     </row>
@@ -16901,15 +16892,12 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L4">
-        <v>26</v>
+        <v>-75</v>
       </c>
       <c r="M4">
-        <v>-75</v>
-      </c>
-      <c r="N4">
         <v>0</v>
       </c>
     </row>
@@ -16945,15 +16933,12 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L5">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="M5">
-        <v>103</v>
-      </c>
-      <c r="N5">
         <v>100</v>
       </c>
     </row>
@@ -16989,15 +16974,12 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L6">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M6">
-        <v>-57</v>
-      </c>
-      <c r="N6">
         <v>0</v>
       </c>
     </row>
@@ -17033,15 +17015,12 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L7">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M7">
-        <v>-57</v>
-      </c>
-      <c r="N7">
         <v>0</v>
       </c>
     </row>
@@ -17077,15 +17056,12 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L8">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M8">
-        <v>-57</v>
-      </c>
-      <c r="N8">
         <v>0</v>
       </c>
     </row>
@@ -17121,15 +17097,12 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L9">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M9">
-        <v>-57</v>
-      </c>
-      <c r="N9">
         <v>0</v>
       </c>
     </row>
@@ -17165,15 +17138,12 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L10">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M10">
-        <v>-57</v>
-      </c>
-      <c r="N10">
         <v>0</v>
       </c>
     </row>
@@ -17209,15 +17179,12 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L11">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M11">
-        <v>-57</v>
-      </c>
-      <c r="N11">
         <v>0</v>
       </c>
     </row>
@@ -17253,15 +17220,12 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L12">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M12">
-        <v>-57</v>
-      </c>
-      <c r="N12">
         <v>0</v>
       </c>
     </row>
@@ -17297,15 +17261,12 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L13">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M13">
-        <v>-57</v>
-      </c>
-      <c r="N13">
         <v>0</v>
       </c>
     </row>
@@ -17341,15 +17302,12 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L14">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M14">
-        <v>-57</v>
-      </c>
-      <c r="N14">
         <v>0</v>
       </c>
     </row>
@@ -17385,15 +17343,12 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L15">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M15">
-        <v>-57</v>
-      </c>
-      <c r="N15">
         <v>0</v>
       </c>
     </row>
@@ -17429,15 +17384,12 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L16">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M16">
-        <v>-57</v>
-      </c>
-      <c r="N16">
         <v>0</v>
       </c>
     </row>
@@ -17473,15 +17425,12 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L17">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M17">
-        <v>-57</v>
-      </c>
-      <c r="N17">
         <v>0</v>
       </c>
     </row>
@@ -17517,15 +17466,12 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L18">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M18">
-        <v>-57</v>
-      </c>
-      <c r="N18">
         <v>0</v>
       </c>
     </row>
@@ -17561,15 +17507,12 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L19">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M19">
-        <v>-57</v>
-      </c>
-      <c r="N19">
         <v>0</v>
       </c>
     </row>
@@ -17605,15 +17548,12 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L20">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M20">
-        <v>-57</v>
-      </c>
-      <c r="N20">
         <v>0</v>
       </c>
     </row>
@@ -17649,15 +17589,12 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L21">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M21">
-        <v>-57</v>
-      </c>
-      <c r="N21">
         <v>0</v>
       </c>
     </row>
@@ -17693,15 +17630,12 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L22">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M22">
-        <v>-57</v>
-      </c>
-      <c r="N22">
         <v>0</v>
       </c>
     </row>
@@ -17737,15 +17671,12 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L23">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M23">
-        <v>-57</v>
-      </c>
-      <c r="N23">
         <v>0</v>
       </c>
     </row>
@@ -17781,15 +17712,12 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L24">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M24">
-        <v>-57</v>
-      </c>
-      <c r="N24">
         <v>0</v>
       </c>
     </row>
@@ -17825,15 +17753,12 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L25">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M25">
-        <v>-57</v>
-      </c>
-      <c r="N25">
         <v>0</v>
       </c>
     </row>
@@ -17869,15 +17794,12 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L26">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M26">
-        <v>-57</v>
-      </c>
-      <c r="N26">
         <v>0</v>
       </c>
     </row>
@@ -17913,15 +17835,12 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L27">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M27">
-        <v>-57</v>
-      </c>
-      <c r="N27">
         <v>0</v>
       </c>
     </row>
@@ -17957,15 +17876,12 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L28">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M28">
-        <v>-57</v>
-      </c>
-      <c r="N28">
         <v>0</v>
       </c>
     </row>
@@ -18001,15 +17917,12 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L29">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M29">
-        <v>-57</v>
-      </c>
-      <c r="N29">
         <v>0</v>
       </c>
     </row>
@@ -18045,15 +17958,12 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L30">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M30">
-        <v>-57</v>
-      </c>
-      <c r="N30">
         <v>0</v>
       </c>
     </row>
@@ -18089,15 +17999,12 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L31">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M31">
-        <v>-57</v>
-      </c>
-      <c r="N31">
         <v>0</v>
       </c>
     </row>
@@ -18133,15 +18040,12 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L32">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M32">
-        <v>-57</v>
-      </c>
-      <c r="N32">
         <v>0</v>
       </c>
     </row>
@@ -18177,15 +18081,12 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L33">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M33">
-        <v>-57</v>
-      </c>
-      <c r="N33">
         <v>0</v>
       </c>
     </row>
@@ -18221,15 +18122,12 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L34">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M34">
-        <v>-57</v>
-      </c>
-      <c r="N34">
         <v>0</v>
       </c>
     </row>
@@ -18265,15 +18163,12 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L35">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M35">
-        <v>-57</v>
-      </c>
-      <c r="N35">
         <v>0</v>
       </c>
     </row>
@@ -18309,15 +18204,12 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L36">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M36">
-        <v>-57</v>
-      </c>
-      <c r="N36">
         <v>0</v>
       </c>
     </row>
@@ -18353,15 +18245,12 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L37">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M37">
-        <v>-57</v>
-      </c>
-      <c r="N37">
         <v>0</v>
       </c>
     </row>
@@ -18397,15 +18286,12 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L38">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M38">
-        <v>-57</v>
-      </c>
-      <c r="N38">
         <v>0</v>
       </c>
     </row>
@@ -18441,15 +18327,12 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L39">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M39">
-        <v>-57</v>
-      </c>
-      <c r="N39">
         <v>0</v>
       </c>
     </row>
@@ -18485,15 +18368,12 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L40">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M40">
-        <v>-57</v>
-      </c>
-      <c r="N40">
         <v>0</v>
       </c>
     </row>
@@ -18529,15 +18409,12 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L41">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M41">
-        <v>-57</v>
-      </c>
-      <c r="N41">
         <v>0</v>
       </c>
     </row>
@@ -18573,15 +18450,12 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L42">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M42">
-        <v>-57</v>
-      </c>
-      <c r="N42">
         <v>0</v>
       </c>
     </row>
@@ -18617,15 +18491,12 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L43">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M43">
-        <v>-57</v>
-      </c>
-      <c r="N43">
         <v>0</v>
       </c>
     </row>
@@ -18661,15 +18532,12 @@
         <v>0</v>
       </c>
       <c r="K44">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L44">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M44">
-        <v>-57</v>
-      </c>
-      <c r="N44">
         <v>0</v>
       </c>
     </row>
@@ -18705,15 +18573,12 @@
         <v>0</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L45">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M45">
-        <v>-57</v>
-      </c>
-      <c r="N45">
         <v>0</v>
       </c>
     </row>
@@ -18749,15 +18614,12 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L46">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M46">
-        <v>-57</v>
-      </c>
-      <c r="N46">
         <v>0</v>
       </c>
     </row>
@@ -18793,15 +18655,12 @@
         <v>0</v>
       </c>
       <c r="K47">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L47">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M47">
-        <v>-57</v>
-      </c>
-      <c r="N47">
         <v>0</v>
       </c>
     </row>
@@ -18837,15 +18696,12 @@
         <v>0</v>
       </c>
       <c r="K48">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L48">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M48">
-        <v>-57</v>
-      </c>
-      <c r="N48">
         <v>0</v>
       </c>
     </row>
@@ -18881,15 +18737,12 @@
         <v>0</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L49">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M49">
-        <v>-57</v>
-      </c>
-      <c r="N49">
         <v>0</v>
       </c>
     </row>
@@ -18925,15 +18778,12 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L50">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M50">
-        <v>-57</v>
-      </c>
-      <c r="N50">
         <v>0</v>
       </c>
     </row>
@@ -18969,15 +18819,12 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L51">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M51">
-        <v>-57</v>
-      </c>
-      <c r="N51">
         <v>0</v>
       </c>
     </row>
@@ -19013,15 +18860,12 @@
         <v>0</v>
       </c>
       <c r="K52">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L52">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M52">
-        <v>-57</v>
-      </c>
-      <c r="N52">
         <v>0</v>
       </c>
     </row>
@@ -19057,15 +18901,12 @@
         <v>0</v>
       </c>
       <c r="K53">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L53">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M53">
-        <v>-57</v>
-      </c>
-      <c r="N53">
         <v>0</v>
       </c>
     </row>
@@ -19101,15 +18942,12 @@
         <v>0</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L54">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M54">
-        <v>-57</v>
-      </c>
-      <c r="N54">
         <v>0</v>
       </c>
     </row>
@@ -19145,15 +18983,12 @@
         <v>0</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L55">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M55">
-        <v>-57</v>
-      </c>
-      <c r="N55">
         <v>0</v>
       </c>
     </row>
@@ -19189,15 +19024,12 @@
         <v>0</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L56">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M56">
-        <v>-57</v>
-      </c>
-      <c r="N56">
         <v>0</v>
       </c>
     </row>
@@ -19233,15 +19065,12 @@
         <v>0</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L57">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M57">
-        <v>-57</v>
-      </c>
-      <c r="N57">
         <v>0</v>
       </c>
     </row>
@@ -19277,15 +19106,12 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L58">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M58">
-        <v>-57</v>
-      </c>
-      <c r="N58">
         <v>0</v>
       </c>
     </row>
@@ -19321,15 +19147,12 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L59">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M59">
-        <v>-57</v>
-      </c>
-      <c r="N59">
         <v>0</v>
       </c>
     </row>
@@ -19365,15 +19188,12 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L60">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M60">
-        <v>-57</v>
-      </c>
-      <c r="N60">
         <v>0</v>
       </c>
     </row>
@@ -19409,15 +19229,12 @@
         <v>0</v>
       </c>
       <c r="K61">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L61">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M61">
-        <v>-57</v>
-      </c>
-      <c r="N61">
         <v>0</v>
       </c>
     </row>
@@ -19453,15 +19270,12 @@
         <v>0</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L62">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M62">
-        <v>-57</v>
-      </c>
-      <c r="N62">
         <v>0</v>
       </c>
     </row>
@@ -19497,15 +19311,12 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L63">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M63">
-        <v>-57</v>
-      </c>
-      <c r="N63">
         <v>0</v>
       </c>
     </row>
@@ -19541,15 +19352,12 @@
         <v>0</v>
       </c>
       <c r="K64">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L64">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M64">
-        <v>-57</v>
-      </c>
-      <c r="N64">
         <v>0</v>
       </c>
     </row>
@@ -19585,15 +19393,12 @@
         <v>0</v>
       </c>
       <c r="K65">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L65">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M65">
-        <v>-57</v>
-      </c>
-      <c r="N65">
         <v>0</v>
       </c>
     </row>
@@ -19629,15 +19434,12 @@
         <v>0</v>
       </c>
       <c r="K66">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L66">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M66">
-        <v>-57</v>
-      </c>
-      <c r="N66">
         <v>0</v>
       </c>
     </row>
@@ -19673,15 +19475,12 @@
         <v>0</v>
       </c>
       <c r="K67">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L67">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M67">
-        <v>-57</v>
-      </c>
-      <c r="N67">
         <v>0</v>
       </c>
     </row>
@@ -19717,15 +19516,12 @@
         <v>0</v>
       </c>
       <c r="K68">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L68">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M68">
-        <v>-57</v>
-      </c>
-      <c r="N68">
         <v>0</v>
       </c>
     </row>
@@ -19761,15 +19557,12 @@
         <v>0</v>
       </c>
       <c r="K69">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L69">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M69">
-        <v>-57</v>
-      </c>
-      <c r="N69">
         <v>0</v>
       </c>
     </row>
@@ -19805,15 +19598,12 @@
         <v>0</v>
       </c>
       <c r="K70">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L70">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M70">
-        <v>-57</v>
-      </c>
-      <c r="N70">
         <v>0</v>
       </c>
     </row>
@@ -19849,15 +19639,12 @@
         <v>0</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L71">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M71">
-        <v>-57</v>
-      </c>
-      <c r="N71">
         <v>0</v>
       </c>
     </row>
@@ -19893,15 +19680,12 @@
         <v>0</v>
       </c>
       <c r="K72">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L72">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M72">
-        <v>-57</v>
-      </c>
-      <c r="N72">
         <v>0</v>
       </c>
     </row>
@@ -19937,15 +19721,12 @@
         <v>0</v>
       </c>
       <c r="K73">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L73">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M73">
-        <v>-57</v>
-      </c>
-      <c r="N73">
         <v>0</v>
       </c>
     </row>
@@ -19981,15 +19762,12 @@
         <v>0</v>
       </c>
       <c r="K74">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L74">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M74">
-        <v>-57</v>
-      </c>
-      <c r="N74">
         <v>0</v>
       </c>
     </row>
@@ -20025,15 +19803,12 @@
         <v>0</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L75">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M75">
-        <v>-57</v>
-      </c>
-      <c r="N75">
         <v>0</v>
       </c>
     </row>
@@ -20069,15 +19844,12 @@
         <v>0</v>
       </c>
       <c r="K76">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L76">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M76">
-        <v>-57</v>
-      </c>
-      <c r="N76">
         <v>0</v>
       </c>
     </row>
@@ -20113,15 +19885,12 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L77">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M77">
-        <v>-57</v>
-      </c>
-      <c r="N77">
         <v>0</v>
       </c>
     </row>
@@ -20157,15 +19926,12 @@
         <v>0</v>
       </c>
       <c r="K78">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L78">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M78">
-        <v>-57</v>
-      </c>
-      <c r="N78">
         <v>0</v>
       </c>
     </row>
@@ -20201,15 +19967,12 @@
         <v>0</v>
       </c>
       <c r="K79">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L79">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M79">
-        <v>-57</v>
-      </c>
-      <c r="N79">
         <v>0</v>
       </c>
     </row>
@@ -20245,15 +20008,12 @@
         <v>0</v>
       </c>
       <c r="K80">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L80">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M80">
-        <v>-57</v>
-      </c>
-      <c r="N80">
         <v>0</v>
       </c>
     </row>
@@ -20289,15 +20049,12 @@
         <v>0</v>
       </c>
       <c r="K81">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L81">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M81">
-        <v>-57</v>
-      </c>
-      <c r="N81">
         <v>0</v>
       </c>
     </row>
@@ -20333,15 +20090,12 @@
         <v>0</v>
       </c>
       <c r="K82">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L82">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M82">
-        <v>-57</v>
-      </c>
-      <c r="N82">
         <v>0</v>
       </c>
     </row>
@@ -20377,15 +20131,12 @@
         <v>0</v>
       </c>
       <c r="K83">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L83">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M83">
-        <v>-57</v>
-      </c>
-      <c r="N83">
         <v>0</v>
       </c>
     </row>
@@ -20421,15 +20172,12 @@
         <v>0</v>
       </c>
       <c r="K84">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L84">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M84">
-        <v>-57</v>
-      </c>
-      <c r="N84">
         <v>0</v>
       </c>
     </row>
@@ -20465,15 +20213,12 @@
         <v>0</v>
       </c>
       <c r="K85">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L85">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M85">
-        <v>-57</v>
-      </c>
-      <c r="N85">
         <v>0</v>
       </c>
     </row>
@@ -20509,15 +20254,12 @@
         <v>0</v>
       </c>
       <c r="K86">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L86">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M86">
-        <v>-57</v>
-      </c>
-      <c r="N86">
         <v>0</v>
       </c>
     </row>
@@ -20553,15 +20295,12 @@
         <v>0</v>
       </c>
       <c r="K87">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L87">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M87">
-        <v>-57</v>
-      </c>
-      <c r="N87">
         <v>0</v>
       </c>
     </row>
@@ -20597,15 +20336,12 @@
         <v>0</v>
       </c>
       <c r="K88">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L88">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M88">
-        <v>-57</v>
-      </c>
-      <c r="N88">
         <v>0</v>
       </c>
     </row>
@@ -20641,15 +20377,12 @@
         <v>0</v>
       </c>
       <c r="K89">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L89">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M89">
-        <v>-57</v>
-      </c>
-      <c r="N89">
         <v>0</v>
       </c>
     </row>
@@ -20685,15 +20418,12 @@
         <v>0</v>
       </c>
       <c r="K90">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L90">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M90">
-        <v>-57</v>
-      </c>
-      <c r="N90">
         <v>0</v>
       </c>
     </row>
@@ -20729,15 +20459,12 @@
         <v>0</v>
       </c>
       <c r="K91">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L91">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M91">
-        <v>-57</v>
-      </c>
-      <c r="N91">
         <v>0</v>
       </c>
     </row>
@@ -20773,15 +20500,12 @@
         <v>0</v>
       </c>
       <c r="K92">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L92">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M92">
-        <v>-57</v>
-      </c>
-      <c r="N92">
         <v>0</v>
       </c>
     </row>
@@ -20817,15 +20541,12 @@
         <v>0</v>
       </c>
       <c r="K93">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L93">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M93">
-        <v>-57</v>
-      </c>
-      <c r="N93">
         <v>0</v>
       </c>
     </row>
@@ -20861,15 +20582,12 @@
         <v>0</v>
       </c>
       <c r="K94">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L94">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M94">
-        <v>-57</v>
-      </c>
-      <c r="N94">
         <v>0</v>
       </c>
     </row>
@@ -20905,15 +20623,12 @@
         <v>0</v>
       </c>
       <c r="K95">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L95">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M95">
-        <v>-57</v>
-      </c>
-      <c r="N95">
         <v>0</v>
       </c>
     </row>
@@ -20949,15 +20664,12 @@
         <v>0</v>
       </c>
       <c r="K96">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L96">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M96">
-        <v>-57</v>
-      </c>
-      <c r="N96">
         <v>0</v>
       </c>
     </row>
@@ -20993,15 +20705,12 @@
         <v>0</v>
       </c>
       <c r="K97">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L97">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M97">
-        <v>-57</v>
-      </c>
-      <c r="N97">
         <v>0</v>
       </c>
     </row>
@@ -21037,15 +20746,12 @@
         <v>0</v>
       </c>
       <c r="K98">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L98">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M98">
-        <v>-57</v>
-      </c>
-      <c r="N98">
         <v>0</v>
       </c>
     </row>
@@ -21081,15 +20787,12 @@
         <v>0</v>
       </c>
       <c r="K99">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L99">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M99">
-        <v>-57</v>
-      </c>
-      <c r="N99">
         <v>0</v>
       </c>
     </row>
@@ -21125,15 +20828,12 @@
         <v>0</v>
       </c>
       <c r="K100">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L100">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M100">
-        <v>-57</v>
-      </c>
-      <c r="N100">
         <v>0</v>
       </c>
     </row>
@@ -21169,15 +20869,12 @@
         <v>0</v>
       </c>
       <c r="K101">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L101">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M101">
-        <v>-57</v>
-      </c>
-      <c r="N101">
         <v>0</v>
       </c>
     </row>
@@ -21213,15 +20910,12 @@
         <v>0</v>
       </c>
       <c r="K102">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L102">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M102">
-        <v>-57</v>
-      </c>
-      <c r="N102">
         <v>0</v>
       </c>
     </row>
@@ -21257,15 +20951,12 @@
         <v>0</v>
       </c>
       <c r="K103">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L103">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M103">
-        <v>-57</v>
-      </c>
-      <c r="N103">
         <v>0</v>
       </c>
     </row>
@@ -21301,15 +20992,12 @@
         <v>0</v>
       </c>
       <c r="K104">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L104">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M104">
-        <v>-57</v>
-      </c>
-      <c r="N104">
         <v>0</v>
       </c>
     </row>
@@ -21345,15 +21033,12 @@
         <v>0</v>
       </c>
       <c r="K105">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L105">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M105">
-        <v>-57</v>
-      </c>
-      <c r="N105">
         <v>0</v>
       </c>
     </row>
@@ -21389,15 +21074,12 @@
         <v>0</v>
       </c>
       <c r="K106">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L106">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M106">
-        <v>-57</v>
-      </c>
-      <c r="N106">
         <v>0</v>
       </c>
     </row>
@@ -21433,15 +21115,12 @@
         <v>0</v>
       </c>
       <c r="K107">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L107">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M107">
-        <v>-57</v>
-      </c>
-      <c r="N107">
         <v>0</v>
       </c>
     </row>
@@ -21477,15 +21156,12 @@
         <v>0</v>
       </c>
       <c r="K108">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L108">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M108">
-        <v>-57</v>
-      </c>
-      <c r="N108">
         <v>0</v>
       </c>
     </row>
@@ -21521,15 +21197,12 @@
         <v>0</v>
       </c>
       <c r="K109">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L109">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M109">
-        <v>-57</v>
-      </c>
-      <c r="N109">
         <v>0</v>
       </c>
     </row>
@@ -21565,15 +21238,12 @@
         <v>0</v>
       </c>
       <c r="K110">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L110">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M110">
-        <v>-57</v>
-      </c>
-      <c r="N110">
         <v>0</v>
       </c>
     </row>
@@ -21609,15 +21279,12 @@
         <v>0</v>
       </c>
       <c r="K111">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L111">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M111">
-        <v>-57</v>
-      </c>
-      <c r="N111">
         <v>0</v>
       </c>
     </row>
@@ -21653,15 +21320,12 @@
         <v>0</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L112">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M112">
-        <v>-57</v>
-      </c>
-      <c r="N112">
         <v>0</v>
       </c>
     </row>
@@ -21697,15 +21361,12 @@
         <v>0</v>
       </c>
       <c r="K113">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L113">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M113">
-        <v>-57</v>
-      </c>
-      <c r="N113">
         <v>0</v>
       </c>
     </row>
@@ -21741,15 +21402,12 @@
         <v>0</v>
       </c>
       <c r="K114">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L114">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M114">
-        <v>-57</v>
-      </c>
-      <c r="N114">
         <v>0</v>
       </c>
     </row>
@@ -21785,15 +21443,12 @@
         <v>0</v>
       </c>
       <c r="K115">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L115">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M115">
-        <v>-57</v>
-      </c>
-      <c r="N115">
         <v>0</v>
       </c>
     </row>
@@ -21829,15 +21484,12 @@
         <v>0</v>
       </c>
       <c r="K116">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L116">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M116">
-        <v>-57</v>
-      </c>
-      <c r="N116">
         <v>0</v>
       </c>
     </row>
@@ -21873,15 +21525,12 @@
         <v>0</v>
       </c>
       <c r="K117">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L117">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M117">
-        <v>-57</v>
-      </c>
-      <c r="N117">
         <v>0</v>
       </c>
     </row>
@@ -21917,15 +21566,12 @@
         <v>0</v>
       </c>
       <c r="K118">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L118">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M118">
-        <v>-57</v>
-      </c>
-      <c r="N118">
         <v>0</v>
       </c>
     </row>
@@ -21961,15 +21607,12 @@
         <v>0</v>
       </c>
       <c r="K119">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L119">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M119">
-        <v>-57</v>
-      </c>
-      <c r="N119">
         <v>0</v>
       </c>
     </row>
@@ -22005,15 +21648,12 @@
         <v>0</v>
       </c>
       <c r="K120">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L120">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M120">
-        <v>-57</v>
-      </c>
-      <c r="N120">
         <v>0</v>
       </c>
     </row>
@@ -22049,15 +21689,12 @@
         <v>0</v>
       </c>
       <c r="K121">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L121">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M121">
-        <v>-57</v>
-      </c>
-      <c r="N121">
         <v>0</v>
       </c>
     </row>
@@ -22093,15 +21730,12 @@
         <v>0</v>
       </c>
       <c r="K122">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L122">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M122">
-        <v>-57</v>
-      </c>
-      <c r="N122">
         <v>0</v>
       </c>
     </row>
@@ -22137,15 +21771,12 @@
         <v>0</v>
       </c>
       <c r="K123">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L123">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M123">
-        <v>-57</v>
-      </c>
-      <c r="N123">
         <v>0</v>
       </c>
     </row>
@@ -22181,15 +21812,12 @@
         <v>0</v>
       </c>
       <c r="K124">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L124">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M124">
-        <v>-57</v>
-      </c>
-      <c r="N124">
         <v>0</v>
       </c>
     </row>
@@ -22225,15 +21853,12 @@
         <v>0</v>
       </c>
       <c r="K125">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L125">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M125">
-        <v>-57</v>
-      </c>
-      <c r="N125">
         <v>0</v>
       </c>
     </row>
@@ -22269,15 +21894,12 @@
         <v>0</v>
       </c>
       <c r="K126">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L126">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M126">
-        <v>-57</v>
-      </c>
-      <c r="N126">
         <v>0</v>
       </c>
     </row>
@@ -22313,15 +21935,12 @@
         <v>0</v>
       </c>
       <c r="K127">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L127">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M127">
-        <v>-57</v>
-      </c>
-      <c r="N127">
         <v>0</v>
       </c>
     </row>
@@ -22357,15 +21976,12 @@
         <v>0</v>
       </c>
       <c r="K128">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L128">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M128">
-        <v>-57</v>
-      </c>
-      <c r="N128">
         <v>0</v>
       </c>
     </row>
@@ -22401,15 +22017,12 @@
         <v>0</v>
       </c>
       <c r="K129">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L129">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M129">
-        <v>-57</v>
-      </c>
-      <c r="N129">
         <v>0</v>
       </c>
     </row>
@@ -22445,15 +22058,12 @@
         <v>0</v>
       </c>
       <c r="K130">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L130">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M130">
-        <v>-57</v>
-      </c>
-      <c r="N130">
         <v>0</v>
       </c>
     </row>
@@ -22489,15 +22099,12 @@
         <v>0</v>
       </c>
       <c r="K131">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L131">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M131">
-        <v>-57</v>
-      </c>
-      <c r="N131">
         <v>0</v>
       </c>
     </row>
@@ -22533,15 +22140,12 @@
         <v>0</v>
       </c>
       <c r="K132">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L132">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M132">
-        <v>-57</v>
-      </c>
-      <c r="N132">
         <v>0</v>
       </c>
     </row>
@@ -22577,15 +22181,12 @@
         <v>0</v>
       </c>
       <c r="K133">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L133">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M133">
-        <v>-57</v>
-      </c>
-      <c r="N133">
         <v>0</v>
       </c>
     </row>
@@ -22621,15 +22222,12 @@
         <v>0</v>
       </c>
       <c r="K134">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L134">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M134">
-        <v>-57</v>
-      </c>
-      <c r="N134">
         <v>0</v>
       </c>
     </row>
@@ -22665,15 +22263,12 @@
         <v>0</v>
       </c>
       <c r="K135">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L135">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M135">
-        <v>-57</v>
-      </c>
-      <c r="N135">
         <v>0</v>
       </c>
     </row>
@@ -22709,15 +22304,12 @@
         <v>0</v>
       </c>
       <c r="K136">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L136">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M136">
-        <v>-57</v>
-      </c>
-      <c r="N136">
         <v>0</v>
       </c>
     </row>
@@ -22753,15 +22345,12 @@
         <v>0</v>
       </c>
       <c r="K137">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L137">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M137">
-        <v>-57</v>
-      </c>
-      <c r="N137">
         <v>0</v>
       </c>
     </row>
@@ -22797,15 +22386,12 @@
         <v>0</v>
       </c>
       <c r="K138">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L138">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M138">
-        <v>-57</v>
-      </c>
-      <c r="N138">
         <v>0</v>
       </c>
     </row>
@@ -22841,15 +22427,12 @@
         <v>0</v>
       </c>
       <c r="K139">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L139">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M139">
-        <v>-57</v>
-      </c>
-      <c r="N139">
         <v>0</v>
       </c>
     </row>
@@ -22885,15 +22468,12 @@
         <v>0</v>
       </c>
       <c r="K140">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L140">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M140">
-        <v>-57</v>
-      </c>
-      <c r="N140">
         <v>0</v>
       </c>
     </row>
@@ -22929,15 +22509,12 @@
         <v>0</v>
       </c>
       <c r="K141">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L141">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M141">
-        <v>-57</v>
-      </c>
-      <c r="N141">
         <v>0</v>
       </c>
     </row>
@@ -22973,15 +22550,12 @@
         <v>0</v>
       </c>
       <c r="K142">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L142">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M142">
-        <v>-57</v>
-      </c>
-      <c r="N142">
         <v>0</v>
       </c>
     </row>
@@ -23017,15 +22591,12 @@
         <v>0</v>
       </c>
       <c r="K143">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L143">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M143">
-        <v>-57</v>
-      </c>
-      <c r="N143">
         <v>0</v>
       </c>
     </row>
@@ -23061,15 +22632,12 @@
         <v>0</v>
       </c>
       <c r="K144">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L144">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M144">
-        <v>-57</v>
-      </c>
-      <c r="N144">
         <v>0</v>
       </c>
     </row>
@@ -23105,15 +22673,12 @@
         <v>0</v>
       </c>
       <c r="K145">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L145">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M145">
-        <v>-57</v>
-      </c>
-      <c r="N145">
         <v>0</v>
       </c>
     </row>
@@ -23149,15 +22714,12 @@
         <v>0</v>
       </c>
       <c r="K146">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L146">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M146">
-        <v>-57</v>
-      </c>
-      <c r="N146">
         <v>0</v>
       </c>
     </row>
@@ -23193,15 +22755,12 @@
         <v>0</v>
       </c>
       <c r="K147">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L147">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M147">
-        <v>-57</v>
-      </c>
-      <c r="N147">
         <v>0</v>
       </c>
     </row>
@@ -23237,15 +22796,12 @@
         <v>0</v>
       </c>
       <c r="K148">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L148">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M148">
-        <v>-57</v>
-      </c>
-      <c r="N148">
         <v>0</v>
       </c>
     </row>
@@ -23281,15 +22837,12 @@
         <v>0</v>
       </c>
       <c r="K149">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L149">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M149">
-        <v>-57</v>
-      </c>
-      <c r="N149">
         <v>0</v>
       </c>
     </row>
@@ -23325,15 +22878,12 @@
         <v>0</v>
       </c>
       <c r="K150">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L150">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M150">
-        <v>-57</v>
-      </c>
-      <c r="N150">
         <v>0</v>
       </c>
     </row>
@@ -23369,15 +22919,12 @@
         <v>0</v>
       </c>
       <c r="K151">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L151">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M151">
-        <v>-57</v>
-      </c>
-      <c r="N151">
         <v>0</v>
       </c>
     </row>
@@ -23413,15 +22960,12 @@
         <v>0</v>
       </c>
       <c r="K152">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L152">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M152">
-        <v>-57</v>
-      </c>
-      <c r="N152">
         <v>0</v>
       </c>
     </row>
@@ -23457,15 +23001,12 @@
         <v>0</v>
       </c>
       <c r="K153">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L153">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M153">
-        <v>-57</v>
-      </c>
-      <c r="N153">
         <v>0</v>
       </c>
     </row>
@@ -23501,15 +23042,12 @@
         <v>0</v>
       </c>
       <c r="K154">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L154">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M154">
-        <v>-57</v>
-      </c>
-      <c r="N154">
         <v>0</v>
       </c>
     </row>
@@ -23545,15 +23083,12 @@
         <v>0</v>
       </c>
       <c r="K155">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L155">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M155">
-        <v>-57</v>
-      </c>
-      <c r="N155">
         <v>0</v>
       </c>
     </row>
@@ -23589,15 +23124,12 @@
         <v>0</v>
       </c>
       <c r="K156">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L156">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M156">
-        <v>-57</v>
-      </c>
-      <c r="N156">
         <v>0</v>
       </c>
     </row>
@@ -23633,15 +23165,12 @@
         <v>0</v>
       </c>
       <c r="K157">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L157">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M157">
-        <v>-57</v>
-      </c>
-      <c r="N157">
         <v>0</v>
       </c>
     </row>
@@ -23677,15 +23206,12 @@
         <v>0</v>
       </c>
       <c r="K158">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L158">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M158">
-        <v>-57</v>
-      </c>
-      <c r="N158">
         <v>0</v>
       </c>
     </row>
@@ -23721,15 +23247,12 @@
         <v>0</v>
       </c>
       <c r="K159">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L159">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M159">
-        <v>-57</v>
-      </c>
-      <c r="N159">
         <v>0</v>
       </c>
     </row>
@@ -23765,15 +23288,12 @@
         <v>0</v>
       </c>
       <c r="K160">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L160">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M160">
-        <v>-57</v>
-      </c>
-      <c r="N160">
         <v>0</v>
       </c>
     </row>
@@ -23809,15 +23329,12 @@
         <v>0</v>
       </c>
       <c r="K161">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L161">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M161">
-        <v>-57</v>
-      </c>
-      <c r="N161">
         <v>0</v>
       </c>
     </row>
@@ -23853,15 +23370,12 @@
         <v>0</v>
       </c>
       <c r="K162">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L162">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M162">
-        <v>-57</v>
-      </c>
-      <c r="N162">
         <v>0</v>
       </c>
     </row>
@@ -23897,15 +23411,12 @@
         <v>0</v>
       </c>
       <c r="K163">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L163">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M163">
-        <v>-57</v>
-      </c>
-      <c r="N163">
         <v>0</v>
       </c>
     </row>
@@ -23941,15 +23452,12 @@
         <v>0</v>
       </c>
       <c r="K164">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L164">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M164">
-        <v>-57</v>
-      </c>
-      <c r="N164">
         <v>0</v>
       </c>
     </row>
@@ -23985,15 +23493,12 @@
         <v>0</v>
       </c>
       <c r="K165">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L165">
-        <v>26</v>
+        <v>-57</v>
       </c>
       <c r="M165">
-        <v>-57</v>
-      </c>
-      <c r="N165">
         <v>0</v>
       </c>
     </row>
@@ -24026,18 +23531,15 @@
         <v>0</v>
       </c>
       <c r="J166">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K166">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L166">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M166">
-        <v>-67</v>
-      </c>
-      <c r="N166">
         <v>0</v>
       </c>
     </row>
@@ -24070,18 +23572,15 @@
         <v>0</v>
       </c>
       <c r="J167">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K167">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L167">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M167">
-        <v>-67</v>
-      </c>
-      <c r="N167">
         <v>0</v>
       </c>
     </row>
@@ -24114,18 +23613,15 @@
         <v>0</v>
       </c>
       <c r="J168">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K168">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L168">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M168">
-        <v>-67</v>
-      </c>
-      <c r="N168">
         <v>0</v>
       </c>
     </row>
@@ -24158,18 +23654,15 @@
         <v>0</v>
       </c>
       <c r="J169">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K169">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L169">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M169">
-        <v>-67</v>
-      </c>
-      <c r="N169">
         <v>0</v>
       </c>
     </row>
@@ -24202,18 +23695,15 @@
         <v>0</v>
       </c>
       <c r="J170">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K170">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L170">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M170">
-        <v>-67</v>
-      </c>
-      <c r="N170">
         <v>0</v>
       </c>
     </row>
@@ -24246,18 +23736,15 @@
         <v>0</v>
       </c>
       <c r="J171">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K171">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L171">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M171">
-        <v>-67</v>
-      </c>
-      <c r="N171">
         <v>0</v>
       </c>
     </row>
@@ -24290,18 +23777,15 @@
         <v>0</v>
       </c>
       <c r="J172">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K172">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L172">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M172">
-        <v>-67</v>
-      </c>
-      <c r="N172">
         <v>0</v>
       </c>
     </row>
@@ -24334,18 +23818,15 @@
         <v>0</v>
       </c>
       <c r="J173">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K173">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L173">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M173">
-        <v>-67</v>
-      </c>
-      <c r="N173">
         <v>0</v>
       </c>
     </row>
@@ -24378,18 +23859,15 @@
         <v>0</v>
       </c>
       <c r="J174">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K174">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L174">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M174">
-        <v>-67</v>
-      </c>
-      <c r="N174">
         <v>0</v>
       </c>
     </row>
@@ -24422,18 +23900,15 @@
         <v>0</v>
       </c>
       <c r="J175">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K175">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L175">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M175">
-        <v>-67</v>
-      </c>
-      <c r="N175">
         <v>0</v>
       </c>
     </row>
@@ -24466,18 +23941,15 @@
         <v>0</v>
       </c>
       <c r="J176">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K176">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L176">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M176">
-        <v>-67</v>
-      </c>
-      <c r="N176">
         <v>0</v>
       </c>
     </row>
@@ -24510,18 +23982,15 @@
         <v>0</v>
       </c>
       <c r="J177">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K177">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L177">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M177">
-        <v>-67</v>
-      </c>
-      <c r="N177">
         <v>0</v>
       </c>
     </row>
@@ -24554,18 +24023,15 @@
         <v>0</v>
       </c>
       <c r="J178">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K178">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L178">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M178">
-        <v>-67</v>
-      </c>
-      <c r="N178">
         <v>0</v>
       </c>
     </row>
@@ -24598,18 +24064,15 @@
         <v>0</v>
       </c>
       <c r="J179">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K179">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L179">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M179">
-        <v>-67</v>
-      </c>
-      <c r="N179">
         <v>0</v>
       </c>
     </row>
@@ -24642,18 +24105,15 @@
         <v>0</v>
       </c>
       <c r="J180">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K180">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L180">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M180">
-        <v>-67</v>
-      </c>
-      <c r="N180">
         <v>0</v>
       </c>
     </row>
@@ -24686,18 +24146,15 @@
         <v>0</v>
       </c>
       <c r="J181">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K181">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L181">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M181">
-        <v>-67</v>
-      </c>
-      <c r="N181">
         <v>0</v>
       </c>
     </row>
@@ -24730,18 +24187,15 @@
         <v>0</v>
       </c>
       <c r="J182">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K182">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L182">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M182">
-        <v>-67</v>
-      </c>
-      <c r="N182">
         <v>0</v>
       </c>
     </row>
@@ -24774,18 +24228,15 @@
         <v>0</v>
       </c>
       <c r="J183">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K183">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L183">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M183">
-        <v>-67</v>
-      </c>
-      <c r="N183">
         <v>0</v>
       </c>
     </row>
@@ -24818,18 +24269,15 @@
         <v>0</v>
       </c>
       <c r="J184">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K184">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L184">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M184">
-        <v>-67</v>
-      </c>
-      <c r="N184">
         <v>0</v>
       </c>
     </row>
@@ -24862,18 +24310,15 @@
         <v>0</v>
       </c>
       <c r="J185">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K185">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L185">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M185">
-        <v>-67</v>
-      </c>
-      <c r="N185">
         <v>0</v>
       </c>
     </row>
@@ -24906,18 +24351,15 @@
         <v>0</v>
       </c>
       <c r="J186">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K186">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L186">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M186">
-        <v>-67</v>
-      </c>
-      <c r="N186">
         <v>0</v>
       </c>
     </row>
@@ -24950,18 +24392,15 @@
         <v>0</v>
       </c>
       <c r="J187">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K187">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L187">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M187">
-        <v>-67</v>
-      </c>
-      <c r="N187">
         <v>0</v>
       </c>
     </row>
@@ -24994,18 +24433,15 @@
         <v>0</v>
       </c>
       <c r="J188">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K188">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L188">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M188">
-        <v>-67</v>
-      </c>
-      <c r="N188">
         <v>0</v>
       </c>
     </row>
@@ -25038,18 +24474,15 @@
         <v>0</v>
       </c>
       <c r="J189">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K189">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L189">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M189">
-        <v>-67</v>
-      </c>
-      <c r="N189">
         <v>0</v>
       </c>
     </row>
@@ -25082,18 +24515,15 @@
         <v>0</v>
       </c>
       <c r="J190">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K190">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L190">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M190">
-        <v>-67</v>
-      </c>
-      <c r="N190">
         <v>0</v>
       </c>
     </row>
@@ -25126,18 +24556,15 @@
         <v>0</v>
       </c>
       <c r="J191">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K191">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L191">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M191">
-        <v>-67</v>
-      </c>
-      <c r="N191">
         <v>0</v>
       </c>
     </row>
@@ -25170,18 +24597,15 @@
         <v>0</v>
       </c>
       <c r="J192">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K192">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L192">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M192">
-        <v>-67</v>
-      </c>
-      <c r="N192">
         <v>0</v>
       </c>
     </row>
@@ -25214,18 +24638,15 @@
         <v>0</v>
       </c>
       <c r="J193">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K193">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L193">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M193">
-        <v>-67</v>
-      </c>
-      <c r="N193">
         <v>0</v>
       </c>
     </row>
@@ -25258,18 +24679,15 @@
         <v>0</v>
       </c>
       <c r="J194">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K194">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L194">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M194">
-        <v>-67</v>
-      </c>
-      <c r="N194">
         <v>0</v>
       </c>
     </row>
@@ -25302,18 +24720,15 @@
         <v>0</v>
       </c>
       <c r="J195">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K195">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L195">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M195">
-        <v>-67</v>
-      </c>
-      <c r="N195">
         <v>0</v>
       </c>
     </row>
@@ -25346,18 +24761,15 @@
         <v>0</v>
       </c>
       <c r="J196">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K196">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L196">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M196">
-        <v>-67</v>
-      </c>
-      <c r="N196">
         <v>0</v>
       </c>
     </row>
@@ -25390,18 +24802,15 @@
         <v>0</v>
       </c>
       <c r="J197">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K197">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L197">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M197">
-        <v>-67</v>
-      </c>
-      <c r="N197">
         <v>0</v>
       </c>
     </row>
@@ -25434,18 +24843,15 @@
         <v>0</v>
       </c>
       <c r="J198">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K198">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L198">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M198">
-        <v>-67</v>
-      </c>
-      <c r="N198">
         <v>0</v>
       </c>
     </row>
@@ -25478,18 +24884,15 @@
         <v>0</v>
       </c>
       <c r="J199">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K199">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L199">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M199">
-        <v>-67</v>
-      </c>
-      <c r="N199">
         <v>0</v>
       </c>
     </row>
@@ -25522,24 +24925,21 @@
         <v>0</v>
       </c>
       <c r="J200">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="K200">
-        <v>-5</v>
+        <v>26</v>
       </c>
       <c r="L200">
-        <v>26</v>
+        <v>-67</v>
       </c>
       <c r="M200">
-        <v>-67</v>
-      </c>
-      <c r="N200">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N200"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M200"/>
   </ignoredErrors>
 </worksheet>
 </file>